--- a/emp_clean.xlsx
+++ b/emp_clean.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://syspoteccol-my.sharepoint.com/personal/sebastian_melo_syspotec_com/Documents/Documentos/empresas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_1405B0B2D3F0512EA170DA734B5ED87656D893F5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{613C1F1E-C019-4C5C-8E63-C2CAD682B7BB}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_1405B0B2D3F0512EA170DA734B5ED87656D893F5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1890C7EB-FA8B-4457-ACD3-A3F407AF78CA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AB$983</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -5233,7 +5236,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -5266,7 +5269,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5282,6 +5285,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -90054,6 +90061,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AB983" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>